--- a/excel/TradeMind_Master_E2E_Report.xlsx
+++ b/excel/TradeMind_Master_E2E_Report.xlsx
@@ -56,7 +56,7 @@
     <t>Report Timestamp</t>
   </si>
   <si>
-    <t>2026-07-31T05:05:16.578Z</t>
+    <t>2026-07-31T05:17:35.625Z</t>
   </si>
   <si>
     <t>Module Name</t>
